--- a/VOYAGES/2026-10-04_KHS1_KMBK_2611N_THLCH_LCH04/2026-10-04_KHS1_KMBK_2611N_THLCH_LCH04.xlsx
+++ b/VOYAGES/2026-10-04_KHS1_KMBK_2611N_THLCH_LCH04/2026-10-04_KHS1_KMBK_2611N_THLCH_LCH04.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>ESCO B3 / LCMT A0/B1</t>
+          <t>LCMT A0/B1</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="26">
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>คำนวณเมื่อ: 04/10/2026 09:05</t>
+          <t>คำนวณเมื่อ: 04/10/2026 09:47</t>
         </is>
       </c>
     </row>
@@ -10562,17 +10562,17 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>LCH01</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>ESCO B3</t>
+          <t>LCMT A0/B1</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
@@ -10675,7 +10675,11 @@
       <c r="AJ67" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AK67" s="12" t="n"/>
+      <c r="AK67" s="12" t="inlineStr">
+        <is>
+          <t>แก้ Location LCH01 → LCH04 (CORRECTIONS.csv: ตู้เข้า LCMT จริงตาม GATE และ BKG LWharf (LOAD/B/L ระบุ LCH01))</t>
+        </is>
+      </c>
       <c r="AL67" s="12" t="inlineStr">
         <is>
           <t>Kanokporn</t>
